--- a/web/files/九龙-启德-天泷.xlsx
+++ b/web/files/九龙-启德-天泷.xlsx
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>635</v>
+        <v>590</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -788,14 +788,14 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
         <v>16383000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>25800</v>
+        <v>27768</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -39259,10 +39259,10 @@
       <c r="C5" s="21" t="inlineStr"/>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>C | 635呎 (3房)
+          <t>C | 590呎 (3房)
 $1638万
-$25,800/呎
-(26年-08月-13日)</t>
+$27,768/呎
+(26年-09月-07日)</t>
         </is>
       </c>
     </row>

--- a/web/files/九龙-启德-天泷.xlsx
+++ b/web/files/九龙-启德-天泷.xlsx
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="E260" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>60360000</v>
       </c>
       <c r="I260" s="5" t="n">
-        <v>47083</v>
+        <v>43676</v>
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
@@ -42278,9 +42278,9 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>B | 1282呎 (4+房)
+          <t>B | 1382呎 (4+房)
 $6036万
-$47,083/呎
+$43,676/呎
 (26年-07月-17日)</t>
         </is>
       </c>

--- a/web/files/九龙-启德-天泷.xlsx
+++ b/web/files/九龙-启德-天泷.xlsx
@@ -36143,23 +36143,19 @@
       </c>
       <c r="F525" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G525" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H525" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I525" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H525" s="5" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="I525" s="5" t="n">
+        <v>40508</v>
       </c>
       <c r="J525" s="3" t="inlineStr">
         <is>
@@ -36168,12 +36164,12 @@
       </c>
       <c r="K525" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L525" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M525" s="3" t="inlineStr">
@@ -36183,7 +36179,7 @@
       </c>
       <c r="N525" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -44757,7 +44753,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -44767,7 +44763,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -45353,12 +45349,12 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
-招标单位
--
-(在售)</t>
+$5100万
+$40,508/呎
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">

--- a/web/files/九龙-启德-天泷.xlsx
+++ b/web/files/九龙-启德-天泷.xlsx
@@ -38335,23 +38335,19 @@
       </c>
       <c r="F557" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G557" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H557" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I557" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="H557" s="5" t="n">
+        <v>46350000</v>
+      </c>
+      <c r="I557" s="5" t="n">
+        <v>36815</v>
       </c>
       <c r="J557" s="3" t="inlineStr">
         <is>
@@ -38360,12 +38356,12 @@
       </c>
       <c r="K557" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L557" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M557" s="3" t="inlineStr">
@@ -38375,7 +38371,7 @@
       </c>
       <c r="N557" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -44753,7 +44749,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -44763,7 +44759,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -45661,12 +45657,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
-招标单位
--
-(在售)</t>
+$4635万
+$36,815/呎
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">

--- a/web/files/九龙-启德-天泷.xlsx
+++ b/web/files/九龙-启德-天泷.xlsx
@@ -1257,7 +1257,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J92" s="3" t="inlineStr">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="N92" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23343,7 +23343,7 @@
       </c>
       <c r="F337" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G337" s="3" t="inlineStr">
@@ -23353,12 +23353,12 @@
       </c>
       <c r="H337" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I337" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J337" s="3" t="inlineStr">
@@ -23368,12 +23368,12 @@
       </c>
       <c r="K337" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L337" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M337" s="3" t="inlineStr">
@@ -23383,7 +23383,7 @@
       </c>
       <c r="N337" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23887,27 +23887,23 @@
         </is>
       </c>
       <c r="E345" s="4" t="n">
-        <v>1102</v>
+        <v>1027</v>
       </c>
       <c r="F345" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H345" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I345" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H345" s="5" t="n">
+        <v>43780000</v>
+      </c>
+      <c r="I345" s="5" t="n">
+        <v>42629</v>
       </c>
       <c r="J345" s="3" t="inlineStr">
         <is>
@@ -23916,12 +23912,12 @@
       </c>
       <c r="K345" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L345" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M345" s="3" t="inlineStr">
@@ -23931,7 +23927,7 @@
       </c>
       <c r="N345" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -28803,7 +28799,7 @@
       </c>
       <c r="F417" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G417" s="3" t="inlineStr">
@@ -28813,12 +28809,12 @@
       </c>
       <c r="H417" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I417" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J417" s="3" t="inlineStr">
@@ -28828,12 +28824,12 @@
       </c>
       <c r="K417" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L417" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M417" s="3" t="inlineStr">
@@ -28843,7 +28839,7 @@
       </c>
       <c r="N417" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -33049,7 +33045,7 @@
       </c>
       <c r="F480" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G480" s="3" t="inlineStr">
@@ -33059,12 +33055,12 @@
       </c>
       <c r="H480" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I480" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J480" s="3" t="inlineStr">
@@ -33074,12 +33070,12 @@
       </c>
       <c r="K480" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L480" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M480" s="3" t="inlineStr">
@@ -33089,7 +33085,7 @@
       </c>
       <c r="N480" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -33119,7 +33115,7 @@
       </c>
       <c r="F481" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G481" s="3" t="inlineStr">
@@ -33129,12 +33125,12 @@
       </c>
       <c r="H481" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I481" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J481" s="3" t="inlineStr">
@@ -33144,12 +33140,12 @@
       </c>
       <c r="K481" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L481" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M481" s="3" t="inlineStr">
@@ -33159,7 +33155,7 @@
       </c>
       <c r="N481" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -35867,7 +35863,7 @@
       </c>
       <c r="F521" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G521" s="3" t="inlineStr">
@@ -35877,12 +35873,12 @@
       </c>
       <c r="H521" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I521" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J521" s="3" t="inlineStr">
@@ -35892,12 +35888,12 @@
       </c>
       <c r="K521" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L521" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M521" s="3" t="inlineStr">
@@ -35907,7 +35903,7 @@
       </c>
       <c r="N521" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -39188,7 +39184,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39203,12 +39199,12 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -39295,12 +39291,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 1428呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -39551,12 +39547,12 @@
 (25年-06月-04日)</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 1258呎 (4+房)
--
--
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -40158,7 +40154,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -40178,7 +40174,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -40274,12 +40270,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 1173呎 (4+房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -40297,12 +40293,12 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 1173呎 (4+房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -42878,7 +42874,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -42888,7 +42884,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -43209,12 +43205,12 @@
 (26年-04月-17日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 1102呎 (3房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -43287,12 +43283,12 @@
 (26年-02月-25日)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>B | 1102呎 (3房)
-招标单位
--
-(在售)</t>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1027呎 (3房)
+$4378万
+$42,629/呎
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -43989,12 +43985,12 @@
 (25年-05月-14日)</t>
         </is>
       </c>
-      <c r="C32" s="23" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>B | 1117呎 (3房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -44749,7 +44745,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -44769,7 +44765,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>59</t>
         </is>
       </c>
     </row>
@@ -44916,20 +44912,20 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -45306,12 +45302,12 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 1259呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">

--- a/web/files/九龙-启德-天泷.xlsx
+++ b/web/files/九龙-启德-天泷.xlsx
@@ -36135,7 +36135,7 @@
         </is>
       </c>
       <c r="E525" s="4" t="n">
-        <v>1259</v>
+        <v>1165</v>
       </c>
       <c r="F525" s="3" t="inlineStr">
         <is>
@@ -36144,14 +36144,14 @@
       </c>
       <c r="G525" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H525" s="5" t="n">
         <v>51000000</v>
       </c>
       <c r="I525" s="5" t="n">
-        <v>40508</v>
+        <v>43777</v>
       </c>
       <c r="J525" s="3" t="inlineStr">
         <is>
@@ -45343,10 +45343,10 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>A | 1259呎 (4+房)
+          <t>A | 1165呎 (4+房)
 $5100万
-$40,508/呎
-(26年-09月-18日)</t>
+$43,777/呎
+(26年-10月-08日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">

--- a/web/files/九龙-启德-天泷.xlsx
+++ b/web/files/九龙-启德-天泷.xlsx
@@ -22791,23 +22791,19 @@
       </c>
       <c r="F329" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H329" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I329" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H329" s="5" t="n">
+        <v>45820000</v>
+      </c>
+      <c r="I329" s="5" t="n">
+        <v>41579</v>
       </c>
       <c r="J329" s="3" t="inlineStr">
         <is>
@@ -22816,12 +22812,12 @@
       </c>
       <c r="K329" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L329" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M329" s="3" t="inlineStr">
@@ -22831,7 +22827,7 @@
       </c>
       <c r="N329" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -22861,23 +22857,19 @@
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H330" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I330" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H330" s="5" t="n">
+        <v>45330000</v>
+      </c>
+      <c r="I330" s="5" t="n">
+        <v>41779</v>
       </c>
       <c r="J330" s="3" t="inlineStr">
         <is>
@@ -22886,12 +22878,12 @@
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L330" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M330" s="3" t="inlineStr">
@@ -22901,7 +22893,7 @@
       </c>
       <c r="N330" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -42874,7 +42866,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -42884,7 +42876,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>41</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -43119,20 +43111,20 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 1085呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
+$4533万
+$41,779/呎
+(26年-10月-12日)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 1102呎 (3房)
-招标单位
--
-(在售)</t>
+$4582万
+$41,579/呎
+(26年-10月-12日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">

--- a/web/files/九龙-启德-天泷.xlsx
+++ b/web/files/九龙-启德-天泷.xlsx
@@ -6535,23 +6535,19 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>40470000</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>43989</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -6560,12 +6556,12 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
@@ -6575,7 +6571,7 @@
       </c>
       <c r="N89" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38319,7 +38315,7 @@
         </is>
       </c>
       <c r="E557" s="4" t="n">
-        <v>1259</v>
+        <v>1165</v>
       </c>
       <c r="F557" s="3" t="inlineStr">
         <is>
@@ -38328,14 +38324,14 @@
       </c>
       <c r="G557" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H557" s="5" t="n">
         <v>46350000</v>
       </c>
       <c r="I557" s="5" t="n">
-        <v>36815</v>
+        <v>39785</v>
       </c>
       <c r="J557" s="3" t="inlineStr">
         <is>
@@ -40146,7 +40142,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -40156,7 +40152,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -40247,12 +40243,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 920呎 (3房)
-招标单位
--
-(在售)</t>
+$4047万
+$43,989/呎
+(26年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -45647,10 +45643,10 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>A | 1259呎 (4+房)
+          <t>A | 1165呎 (4+房)
 $4635万
-$36,815/呎
-(26年-09月-22日)</t>
+$39,785/呎
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">

--- a/web/files/九龙-启德-天泷.xlsx
+++ b/web/files/九龙-启德-天泷.xlsx
@@ -23884,7 +23884,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -29413,23 +29413,19 @@
       </c>
       <c r="F426" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H426" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I426" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="H426" s="5" t="n">
+        <v>42500000</v>
+      </c>
+      <c r="I426" s="5" t="n">
+        <v>42415</v>
       </c>
       <c r="J426" s="3" t="inlineStr">
         <is>
@@ -29438,12 +29434,12 @@
       </c>
       <c r="K426" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L426" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M426" s="3" t="inlineStr">
@@ -29453,7 +29449,7 @@
       </c>
       <c r="N426" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -37973,23 +37969,19 @@
       </c>
       <c r="F552" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G552" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H552" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I552" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="H552" s="5" t="n">
+        <v>48160000</v>
+      </c>
+      <c r="I552" s="5" t="n">
+        <v>37103</v>
       </c>
       <c r="J552" s="3" t="inlineStr">
         <is>
@@ -37998,12 +37990,12 @@
       </c>
       <c r="K552" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L552" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M552" s="3" t="inlineStr">
@@ -38013,7 +38005,7 @@
       </c>
       <c r="N552" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -43276,7 +43268,7 @@
           <t>B | 1027呎 (3房)
 $4378万
 $42,629/呎
-(26年-09月-29日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -44068,7 +44060,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -44078,7 +44070,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -44184,12 +44176,12 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 1002呎 (3房)
-招标单位
--
-(在售)</t>
+$4250万
+$42,415/呎
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
@@ -44733,7 +44725,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -44743,7 +44735,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -45610,12 +45602,12 @@
 (26年-01月-27日)</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
-招标单位
--
-(在售)</t>
+$4816万
+$37,103/呎
+(26年-10月-27日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">

--- a/web/files/九龙-启德-天泷.xlsx
+++ b/web/files/九龙-启德-天泷.xlsx
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>16383000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>27768</v>
+        <v>25800</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>16165500</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>27399</v>
+        <v>25457</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>15680000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>26576</v>
+        <v>24693</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>15875000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>26907</v>
+        <v>25000</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>15398700</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>26099</v>
+        <v>24250</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>15748000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>26692</v>
+        <v>24800</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>67400000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>50336</v>
+        <v>47199</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>15684500</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>26584</v>
+        <v>24700</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>66650000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>49776</v>
+        <v>46674</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>15621000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>26476</v>
+        <v>24600</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>60070000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>44862</v>
+        <v>42066</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>15090700</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>25577</v>
+        <v>23765</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1171</v>
+        <v>1258</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>52850000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>45132</v>
+        <v>42011</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>64530000</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>48193</v>
+        <v>45189</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>14968000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>25369</v>
+        <v>23572</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1171</v>
+        <v>1258</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>48680000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>41571</v>
+        <v>38696</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>15367000</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>26046</v>
+        <v>24200</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>58100000</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>43391</v>
+        <v>40686</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>14906000</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>25264</v>
+        <v>23474</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>1171</v>
+        <v>1258</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>49000000</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>41845</v>
+        <v>38951</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>61610000</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>46012</v>
+        <v>43144</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>15240000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>25831</v>
+        <v>24000</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1171</v>
+        <v>1258</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>47560000</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>40615</v>
+        <v>37806</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>14647000</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>24825</v>
+        <v>23066</v>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1171</v>
+        <v>1258</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>47190000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>40299</v>
+        <v>37512</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>58320000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>43555</v>
+        <v>40840</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3549,7 +3549,7 @@
         <v>15113000</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>25615</v>
+        <v>23800</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>59760000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>44630</v>
+        <v>41849</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>14859000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>25185</v>
+        <v>23400</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>1171</v>
+        <v>1258</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>45680000</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>39009</v>
+        <v>36312</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>14610080</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>24763</v>
+        <v>23008</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>1171</v>
+        <v>1258</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
         <v>45020000</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>38446</v>
+        <v>35787</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>55500000</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>41449</v>
+        <v>38866</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>14050000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>23814</v>
+        <v>22126</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>14401800</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>24410</v>
+        <v>22680</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1171</v>
+        <v>1258</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>47900000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>40905</v>
+        <v>38076</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -4485,7 +4485,7 @@
         <v>56570000</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>42248</v>
+        <v>39615</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>14224000</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>24108</v>
+        <v>22400</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1171</v>
+        <v>1258</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         <v>47630000</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>40675</v>
+        <v>37862</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>14160500</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>24001</v>
+        <v>22300</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1171</v>
+        <v>1258</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         <v>47110000</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>40231</v>
+        <v>37448</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>54675000</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>40833</v>
+        <v>38288</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>14097000</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>23893</v>
+        <v>22200</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1171</v>
+        <v>1258</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>45100000</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>38514</v>
+        <v>35851</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -5063,7 +5063,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         <v>55580000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>41509</v>
+        <v>38922</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>14065250</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>23839</v>
+        <v>22150</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>1171</v>
+        <v>1258</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>44930000</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>38369</v>
+        <v>35715</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>55460000</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>41419</v>
+        <v>38838</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>13612500</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>23072</v>
+        <v>21437</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -5393,7 +5393,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>1171</v>
+        <v>1258</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>45570000</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>38915</v>
+        <v>36224</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>53650000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>40067</v>
+        <v>37570</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>13970000</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>23678</v>
+        <v>22000</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>1171</v>
+        <v>1258</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         <v>44080000</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>37643</v>
+        <v>35040</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5673,7 +5673,7 @@
         <v>54320000</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>40568</v>
+        <v>38039</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>13490000</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>22864</v>
+        <v>21244</v>
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>1171</v>
+        <v>1258</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>43790000</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>37395</v>
+        <v>34809</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>53928000</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>40275</v>
+        <v>37765</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>590</v>
+        <v>635</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>13243000</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>22446</v>
+        <v>20855</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>1171</v>
+        <v>1258</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>44600000</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>38087</v>
+        <v>35453</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>53270000</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>39783</v>
+        <v>37304</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         </is>
       </c>
       <c r="E83" s="4" t="n">
-        <v>1171</v>
+        <v>1258</v>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>44120000</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>37677</v>
+        <v>35072</v>
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>1339</v>
+        <v>1428</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>52230000</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>39007</v>
+        <v>36576</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>40470000</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>43989</v>
+        <v>40389</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="E91" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>39820000</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>43283</v>
+        <v>39741</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         </is>
       </c>
       <c r="E93" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>38890000</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>42272</v>
+        <v>38812</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>36380000</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>39543</v>
+        <v>36307</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>36100000</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>39239</v>
+        <v>36028</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>34540000</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>37543</v>
+        <v>34471</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         <v>45900000</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>42658</v>
+        <v>39130</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>45520000</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>42305</v>
+        <v>38806</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
         <v>33060000</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>35935</v>
+        <v>32994</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="E108" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>43880000</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>40781</v>
+        <v>37408</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>43650000</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>40567</v>
+        <v>37212</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>33030000</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>35902</v>
+        <v>32964</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
@@ -8221,7 +8221,7 @@
         <v>40380000</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>37528</v>
+        <v>34425</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
@@ -8667,7 +8667,7 @@
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
         <v>31400000</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>34130</v>
+        <v>31337</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>32190000</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>34989</v>
+        <v>32126</v>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="E130" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>38360000</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>35651</v>
+        <v>32702</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>31380000</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>34109</v>
+        <v>31317</v>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="E133" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>30440000</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>33087</v>
+        <v>30379</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         </is>
       </c>
       <c r="E135" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>30320000</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>32957</v>
+        <v>30259</v>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         </is>
       </c>
       <c r="E136" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>37301400</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>34667</v>
+        <v>31800</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="E137" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>30280000</v>
       </c>
       <c r="I137" s="5" t="n">
-        <v>32913</v>
+        <v>30220</v>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>37150000</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>34526</v>
+        <v>31671</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
@@ -9921,7 +9921,7 @@
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>36510000</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>33931</v>
+        <v>31125</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         </is>
       </c>
       <c r="E166" s="4" t="n">
-        <v>994</v>
+        <v>1085</v>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
@@ -11741,7 +11741,7 @@
         <v>40600000</v>
       </c>
       <c r="I166" s="5" t="n">
-        <v>40845</v>
+        <v>37419</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="E170" s="4" t="n">
-        <v>994</v>
+        <v>1085</v>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>38600000</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>38833</v>
+        <v>35576</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         </is>
       </c>
       <c r="E171" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>41632000</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>40537</v>
+        <v>37779</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         </is>
       </c>
       <c r="E175" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>37740000</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>36748</v>
+        <v>34247</v>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         </is>
       </c>
       <c r="E178" s="4" t="n">
-        <v>994</v>
+        <v>1085</v>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>37520000</v>
       </c>
       <c r="I178" s="5" t="n">
-        <v>37746</v>
+        <v>34581</v>
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         </is>
       </c>
       <c r="E182" s="4" t="n">
-        <v>994</v>
+        <v>1085</v>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>36600000</v>
       </c>
       <c r="I182" s="5" t="n">
-        <v>36821</v>
+        <v>33733</v>
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="E183" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>36800000</v>
       </c>
       <c r="I183" s="5" t="n">
-        <v>35833</v>
+        <v>33394</v>
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         </is>
       </c>
       <c r="E190" s="4" t="n">
-        <v>994</v>
+        <v>1085</v>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>49600000</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>49899</v>
+        <v>45714</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         </is>
       </c>
       <c r="E191" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>41139000</v>
       </c>
       <c r="I191" s="5" t="n">
-        <v>40057</v>
+        <v>37331</v>
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
@@ -13633,7 +13633,7 @@
         </is>
       </c>
       <c r="E194" s="4" t="n">
-        <v>994</v>
+        <v>1085</v>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
@@ -13649,7 +13649,7 @@
         <v>36290000</v>
       </c>
       <c r="I194" s="5" t="n">
-        <v>36509</v>
+        <v>33447</v>
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         </is>
       </c>
       <c r="E203" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
@@ -14259,7 +14259,7 @@
         <v>35840000</v>
       </c>
       <c r="I203" s="5" t="n">
-        <v>34898</v>
+        <v>32523</v>
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         </is>
       </c>
       <c r="E207" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>35630000</v>
       </c>
       <c r="I207" s="5" t="n">
-        <v>34693</v>
+        <v>32332</v>
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="E210" s="4" t="n">
-        <v>994</v>
+        <v>1085</v>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>35397600</v>
       </c>
       <c r="I210" s="5" t="n">
-        <v>35611</v>
+        <v>32625</v>
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         </is>
       </c>
       <c r="E211" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>35930000</v>
       </c>
       <c r="I211" s="5" t="n">
-        <v>34985</v>
+        <v>32604</v>
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         </is>
       </c>
       <c r="E222" s="4" t="n">
-        <v>994</v>
+        <v>1085</v>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>35550000</v>
       </c>
       <c r="I222" s="5" t="n">
-        <v>35765</v>
+        <v>32765</v>
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         </is>
       </c>
       <c r="E223" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>38800000</v>
       </c>
       <c r="I223" s="5" t="n">
-        <v>37780</v>
+        <v>35209</v>
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
@@ -15809,7 +15809,7 @@
         </is>
       </c>
       <c r="E226" s="4" t="n">
-        <v>994</v>
+        <v>1085</v>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>34535200</v>
       </c>
       <c r="I226" s="5" t="n">
-        <v>34744</v>
+        <v>31830</v>
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         </is>
       </c>
       <c r="E242" s="4" t="n">
-        <v>994</v>
+        <v>1085</v>
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>33510000</v>
       </c>
       <c r="I242" s="5" t="n">
-        <v>33712</v>
+        <v>30885</v>
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         </is>
       </c>
       <c r="E247" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>33230000</v>
       </c>
       <c r="I247" s="5" t="n">
-        <v>32356</v>
+        <v>30154</v>
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
@@ -17441,7 +17441,7 @@
         </is>
       </c>
       <c r="E250" s="4" t="n">
-        <v>994</v>
+        <v>1085</v>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>35300000</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>35513</v>
+        <v>32535</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         </is>
       </c>
       <c r="E262" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F262" s="3" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>59820000</v>
       </c>
       <c r="I262" s="5" t="n">
-        <v>46661</v>
+        <v>43285</v>
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         </is>
       </c>
       <c r="E265" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>55910000</v>
       </c>
       <c r="I265" s="5" t="n">
-        <v>43612</v>
+        <v>40456</v>
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         </is>
       </c>
       <c r="E268" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F268" s="3" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>54320000</v>
       </c>
       <c r="I268" s="5" t="n">
-        <v>42371</v>
+        <v>39305</v>
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         </is>
       </c>
       <c r="E272" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>52263400</v>
       </c>
       <c r="I272" s="5" t="n">
-        <v>40767</v>
+        <v>37817</v>
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         </is>
       </c>
       <c r="E274" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>51950000</v>
       </c>
       <c r="I274" s="5" t="n">
-        <v>40523</v>
+        <v>37590</v>
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         </is>
       </c>
       <c r="E275" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>51950000</v>
       </c>
       <c r="I275" s="5" t="n">
-        <v>40523</v>
+        <v>37590</v>
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         </is>
       </c>
       <c r="E279" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>52458000</v>
       </c>
       <c r="I279" s="5" t="n">
-        <v>40919</v>
+        <v>37958</v>
       </c>
       <c r="J279" s="3" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         </is>
       </c>
       <c r="E281" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
@@ -19547,7 +19547,7 @@
         <v>54280000</v>
       </c>
       <c r="I281" s="5" t="n">
-        <v>42340</v>
+        <v>39276</v>
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
@@ -19861,7 +19861,7 @@
         </is>
       </c>
       <c r="E286" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>50700000</v>
       </c>
       <c r="I286" s="5" t="n">
-        <v>39548</v>
+        <v>36686</v>
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         </is>
       </c>
       <c r="E287" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>50700000</v>
       </c>
       <c r="I287" s="5" t="n">
-        <v>39548</v>
+        <v>36686</v>
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         </is>
       </c>
       <c r="E288" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>50600000</v>
       </c>
       <c r="I288" s="5" t="n">
-        <v>39470</v>
+        <v>36614</v>
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         </is>
       </c>
       <c r="E289" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
@@ -20075,7 +20075,7 @@
         <v>49810000</v>
       </c>
       <c r="I289" s="5" t="n">
-        <v>38853</v>
+        <v>36042</v>
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         </is>
       </c>
       <c r="E290" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>50500000</v>
       </c>
       <c r="I290" s="5" t="n">
-        <v>39392</v>
+        <v>36541</v>
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         </is>
       </c>
       <c r="E291" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>50500000</v>
       </c>
       <c r="I291" s="5" t="n">
-        <v>39392</v>
+        <v>36541</v>
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         </is>
       </c>
       <c r="E292" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>48980000</v>
       </c>
       <c r="I292" s="5" t="n">
-        <v>38206</v>
+        <v>35441</v>
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         </is>
       </c>
       <c r="E293" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>48980000</v>
       </c>
       <c r="I293" s="5" t="n">
-        <v>38206</v>
+        <v>35441</v>
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="E295" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>49950000</v>
       </c>
       <c r="I295" s="5" t="n">
-        <v>38963</v>
+        <v>36143</v>
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
@@ -20521,7 +20521,7 @@
         </is>
       </c>
       <c r="E296" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>49660000</v>
       </c>
       <c r="I296" s="5" t="n">
-        <v>38736</v>
+        <v>35933</v>
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         </is>
       </c>
       <c r="E297" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>49660000</v>
       </c>
       <c r="I297" s="5" t="n">
-        <v>38736</v>
+        <v>35933</v>
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         </is>
       </c>
       <c r="E298" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>49080000</v>
       </c>
       <c r="I298" s="5" t="n">
-        <v>38284</v>
+        <v>35514</v>
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         </is>
       </c>
       <c r="E299" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>49080000</v>
       </c>
       <c r="I299" s="5" t="n">
-        <v>38284</v>
+        <v>35514</v>
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         </is>
       </c>
       <c r="E300" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>48190000</v>
       </c>
       <c r="I300" s="5" t="n">
-        <v>37590</v>
+        <v>34870</v>
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         </is>
       </c>
       <c r="E301" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
@@ -20867,7 +20867,7 @@
         <v>48138000</v>
       </c>
       <c r="I301" s="5" t="n">
-        <v>37549</v>
+        <v>34832</v>
       </c>
       <c r="J301" s="3" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         </is>
       </c>
       <c r="E302" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F302" s="3" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>49610000</v>
       </c>
       <c r="I302" s="5" t="n">
-        <v>38697</v>
+        <v>35897</v>
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         </is>
       </c>
       <c r="E303" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
@@ -20999,7 +20999,7 @@
         <v>48450000</v>
       </c>
       <c r="I303" s="5" t="n">
-        <v>37793</v>
+        <v>35058</v>
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
@@ -21049,7 +21049,7 @@
         </is>
       </c>
       <c r="E304" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F304" s="3" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>47530000</v>
       </c>
       <c r="I304" s="5" t="n">
-        <v>37075</v>
+        <v>34392</v>
       </c>
       <c r="J304" s="3" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         </is>
       </c>
       <c r="E305" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F305" s="3" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>48820000</v>
       </c>
       <c r="I305" s="5" t="n">
-        <v>38081</v>
+        <v>35326</v>
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         </is>
       </c>
       <c r="E306" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>48770000</v>
       </c>
       <c r="I306" s="5" t="n">
-        <v>38042</v>
+        <v>35289</v>
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         </is>
       </c>
       <c r="E307" s="4" t="n">
-        <v>1282</v>
+        <v>1382</v>
       </c>
       <c r="F307" s="3" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>48680000</v>
       </c>
       <c r="I307" s="5" t="n">
-        <v>37972</v>
+        <v>35224</v>
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         </is>
       </c>
       <c r="E333" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F333" s="3" t="inlineStr">
         <is>
@@ -23071,7 +23071,7 @@
         <v>45180000</v>
       </c>
       <c r="I333" s="5" t="n">
-        <v>43992</v>
+        <v>40998</v>
       </c>
       <c r="J333" s="3" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         </is>
       </c>
       <c r="E334" s="4" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="F334" s="3" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>44690000</v>
       </c>
       <c r="I334" s="5" t="n">
-        <v>45050</v>
+        <v>41189</v>
       </c>
       <c r="J334" s="3" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         </is>
       </c>
       <c r="E338" s="4" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="F338" s="3" t="inlineStr">
         <is>
@@ -23413,7 +23413,7 @@
         <v>44050000</v>
       </c>
       <c r="I338" s="5" t="n">
-        <v>44405</v>
+        <v>40599</v>
       </c>
       <c r="J338" s="3" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         </is>
       </c>
       <c r="E341" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F341" s="3" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>44270000</v>
       </c>
       <c r="I341" s="5" t="n">
-        <v>43106</v>
+        <v>40172</v>
       </c>
       <c r="J341" s="3" t="inlineStr">
         <is>
@@ -23669,7 +23669,7 @@
         </is>
       </c>
       <c r="E342" s="4" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="F342" s="3" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>43410000</v>
       </c>
       <c r="I342" s="5" t="n">
-        <v>43760</v>
+        <v>40009</v>
       </c>
       <c r="J342" s="3" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="E345" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F345" s="3" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>43780000</v>
       </c>
       <c r="I345" s="5" t="n">
-        <v>42629</v>
+        <v>39728</v>
       </c>
       <c r="J345" s="3" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         </is>
       </c>
       <c r="E346" s="4" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="F346" s="3" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>42170000</v>
       </c>
       <c r="I346" s="5" t="n">
-        <v>42510</v>
+        <v>38866</v>
       </c>
       <c r="J346" s="3" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         </is>
       </c>
       <c r="E349" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F349" s="3" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>43000000</v>
       </c>
       <c r="I349" s="5" t="n">
-        <v>41870</v>
+        <v>39020</v>
       </c>
       <c r="J349" s="3" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         </is>
       </c>
       <c r="E350" s="4" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="F350" s="3" t="inlineStr">
         <is>
@@ -24229,7 +24229,7 @@
         <v>38650000</v>
       </c>
       <c r="I350" s="5" t="n">
-        <v>38962</v>
+        <v>35622</v>
       </c>
       <c r="J350" s="3" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         </is>
       </c>
       <c r="E353" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F353" s="3" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         <v>38850000</v>
       </c>
       <c r="I353" s="5" t="n">
-        <v>37829</v>
+        <v>35254</v>
       </c>
       <c r="J353" s="3" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         </is>
       </c>
       <c r="E354" s="4" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>38430000</v>
       </c>
       <c r="I354" s="5" t="n">
-        <v>38740</v>
+        <v>35419</v>
       </c>
       <c r="J354" s="3" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         </is>
       </c>
       <c r="E357" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
@@ -24707,7 +24707,7 @@
         <v>41290000</v>
       </c>
       <c r="I357" s="5" t="n">
-        <v>40204</v>
+        <v>37468</v>
       </c>
       <c r="J357" s="3" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         </is>
       </c>
       <c r="E358" s="4" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="F358" s="3" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>38980000</v>
       </c>
       <c r="I358" s="5" t="n">
-        <v>39294</v>
+        <v>35926</v>
       </c>
       <c r="J358" s="3" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         </is>
       </c>
       <c r="E361" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F361" s="3" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>39350000</v>
       </c>
       <c r="I361" s="5" t="n">
-        <v>38315</v>
+        <v>35708</v>
       </c>
       <c r="J361" s="3" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         </is>
       </c>
       <c r="E362" s="4" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>38200000</v>
       </c>
       <c r="I362" s="5" t="n">
-        <v>38508</v>
+        <v>35207</v>
       </c>
       <c r="J362" s="3" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         </is>
       </c>
       <c r="E365" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F365" s="3" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>38780000</v>
       </c>
       <c r="I365" s="5" t="n">
-        <v>37760</v>
+        <v>35191</v>
       </c>
       <c r="J365" s="3" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         </is>
       </c>
       <c r="E366" s="4" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>38180000</v>
       </c>
       <c r="I366" s="5" t="n">
-        <v>38488</v>
+        <v>35189</v>
       </c>
       <c r="J366" s="3" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         </is>
       </c>
       <c r="E373" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F373" s="3" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>37800000</v>
       </c>
       <c r="I373" s="5" t="n">
-        <v>36806</v>
+        <v>34301</v>
       </c>
       <c r="J373" s="3" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         </is>
       </c>
       <c r="E374" s="4" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="F374" s="3" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>37400000</v>
       </c>
       <c r="I374" s="5" t="n">
-        <v>37702</v>
+        <v>34470</v>
       </c>
       <c r="J374" s="3" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         </is>
       </c>
       <c r="E377" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F377" s="3" t="inlineStr">
         <is>
@@ -26075,7 +26075,7 @@
         <v>37000000</v>
       </c>
       <c r="I377" s="5" t="n">
-        <v>36027</v>
+        <v>33575</v>
       </c>
       <c r="J377" s="3" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         </is>
       </c>
       <c r="E378" s="4" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>37300000</v>
       </c>
       <c r="I378" s="5" t="n">
-        <v>37601</v>
+        <v>34378</v>
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         </is>
       </c>
       <c r="E381" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F381" s="3" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>37280000</v>
       </c>
       <c r="I381" s="5" t="n">
-        <v>36300</v>
+        <v>33829</v>
       </c>
       <c r="J381" s="3" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         </is>
       </c>
       <c r="E382" s="4" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>36790000</v>
       </c>
       <c r="I382" s="5" t="n">
-        <v>37087</v>
+        <v>33908</v>
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         </is>
       </c>
       <c r="E385" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F385" s="3" t="inlineStr">
         <is>
@@ -26619,7 +26619,7 @@
         <v>36400000</v>
       </c>
       <c r="I385" s="5" t="n">
-        <v>35443</v>
+        <v>33031</v>
       </c>
       <c r="J385" s="3" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         </is>
       </c>
       <c r="E386" s="4" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="F386" s="3" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>36000000</v>
       </c>
       <c r="I386" s="5" t="n">
-        <v>36290</v>
+        <v>33180</v>
       </c>
       <c r="J386" s="3" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         </is>
       </c>
       <c r="E394" s="4" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="F394" s="3" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>35650000</v>
       </c>
       <c r="I394" s="5" t="n">
-        <v>35938</v>
+        <v>32857</v>
       </c>
       <c r="J394" s="3" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         </is>
       </c>
       <c r="E397" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F397" s="3" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>36640000</v>
       </c>
       <c r="I397" s="5" t="n">
-        <v>35677</v>
+        <v>33249</v>
       </c>
       <c r="J397" s="3" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         </is>
       </c>
       <c r="E398" s="4" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="F398" s="3" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>36260000</v>
       </c>
       <c r="I398" s="5" t="n">
-        <v>36552</v>
+        <v>33419</v>
       </c>
       <c r="J398" s="3" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         </is>
       </c>
       <c r="E401" s="4" t="n">
-        <v>1027</v>
+        <v>1102</v>
       </c>
       <c r="F401" s="3" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>36530000</v>
       </c>
       <c r="I401" s="5" t="n">
-        <v>35570</v>
+        <v>33149</v>
       </c>
       <c r="J401" s="3" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         </is>
       </c>
       <c r="E402" s="4" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>34530000</v>
       </c>
       <c r="I402" s="5" t="n">
-        <v>34808</v>
+        <v>31825</v>
       </c>
       <c r="J402" s="3" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         </is>
       </c>
       <c r="E405" s="4" t="n">
-        <v>1042</v>
+        <v>1117</v>
       </c>
       <c r="F405" s="3" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>37710000</v>
       </c>
       <c r="I405" s="5" t="n">
-        <v>36190</v>
+        <v>33760</v>
       </c>
       <c r="J405" s="3" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         </is>
       </c>
       <c r="E406" s="4" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="F406" s="3" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>32740000</v>
       </c>
       <c r="I406" s="5" t="n">
-        <v>33004</v>
+        <v>30175</v>
       </c>
       <c r="J406" s="3" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         </is>
       </c>
       <c r="E409" s="4" t="n">
-        <v>1042</v>
+        <v>1117</v>
       </c>
       <c r="F409" s="3" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>31930000</v>
       </c>
       <c r="I409" s="5" t="n">
-        <v>30643</v>
+        <v>28585</v>
       </c>
       <c r="J409" s="3" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         </is>
       </c>
       <c r="E414" s="4" t="n">
-        <v>992</v>
+        <v>1085</v>
       </c>
       <c r="F414" s="3" t="inlineStr">
         <is>
@@ -28593,7 +28593,7 @@
         <v>31840000</v>
       </c>
       <c r="I414" s="5" t="n">
-        <v>32097</v>
+        <v>29346</v>
       </c>
       <c r="J414" s="3" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         </is>
       </c>
       <c r="E428" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F428" s="3" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>41110000</v>
       </c>
       <c r="I428" s="5" t="n">
-        <v>44685</v>
+        <v>41028</v>
       </c>
       <c r="J428" s="3" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         </is>
       </c>
       <c r="E429" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F429" s="3" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>46360000</v>
       </c>
       <c r="I429" s="5" t="n">
-        <v>43086</v>
+        <v>39523</v>
       </c>
       <c r="J429" s="3" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         </is>
       </c>
       <c r="E430" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F430" s="3" t="inlineStr">
         <is>
@@ -29693,7 +29693,7 @@
         <v>38350000</v>
       </c>
       <c r="I430" s="5" t="n">
-        <v>41685</v>
+        <v>38273</v>
       </c>
       <c r="J430" s="3" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         </is>
       </c>
       <c r="E431" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F431" s="3" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>44300000</v>
       </c>
       <c r="I431" s="5" t="n">
-        <v>41171</v>
+        <v>37766</v>
       </c>
       <c r="J431" s="3" t="inlineStr">
         <is>
@@ -29809,7 +29809,7 @@
         </is>
       </c>
       <c r="E432" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         <v>36750000</v>
       </c>
       <c r="I432" s="5" t="n">
-        <v>39946</v>
+        <v>36677</v>
       </c>
       <c r="J432" s="3" t="inlineStr">
         <is>
@@ -29875,7 +29875,7 @@
         </is>
       </c>
       <c r="E433" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F433" s="3" t="inlineStr">
         <is>
@@ -29891,7 +29891,7 @@
         <v>44050000</v>
       </c>
       <c r="I433" s="5" t="n">
-        <v>40939</v>
+        <v>37553</v>
       </c>
       <c r="J433" s="3" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         </is>
       </c>
       <c r="E434" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F434" s="3" t="inlineStr">
         <is>
@@ -29957,7 +29957,7 @@
         <v>36430000</v>
       </c>
       <c r="I434" s="5" t="n">
-        <v>39598</v>
+        <v>36357</v>
       </c>
       <c r="J434" s="3" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         </is>
       </c>
       <c r="E437" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F437" s="3" t="inlineStr">
         <is>
@@ -30155,7 +30155,7 @@
         <v>43450000</v>
       </c>
       <c r="I437" s="5" t="n">
-        <v>40381</v>
+        <v>37042</v>
       </c>
       <c r="J437" s="3" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         </is>
       </c>
       <c r="E438" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F438" s="3" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>35800000</v>
       </c>
       <c r="I438" s="5" t="n">
-        <v>38913</v>
+        <v>35729</v>
       </c>
       <c r="J438" s="3" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         </is>
       </c>
       <c r="E439" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F439" s="3" t="inlineStr">
         <is>
@@ -30287,7 +30287,7 @@
         <v>42980000</v>
       </c>
       <c r="I439" s="5" t="n">
-        <v>39944</v>
+        <v>36641</v>
       </c>
       <c r="J439" s="3" t="inlineStr">
         <is>
@@ -30337,7 +30337,7 @@
         </is>
       </c>
       <c r="E440" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F440" s="3" t="inlineStr">
         <is>
@@ -30353,7 +30353,7 @@
         <v>35340000</v>
       </c>
       <c r="I440" s="5" t="n">
-        <v>38413</v>
+        <v>35269</v>
       </c>
       <c r="J440" s="3" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         </is>
       </c>
       <c r="E442" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F442" s="3" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>34720000</v>
       </c>
       <c r="I442" s="5" t="n">
-        <v>37739</v>
+        <v>34651</v>
       </c>
       <c r="J442" s="3" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         </is>
       </c>
       <c r="E443" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F443" s="3" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>42460000</v>
       </c>
       <c r="I443" s="5" t="n">
-        <v>39461</v>
+        <v>36198</v>
       </c>
       <c r="J443" s="3" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         </is>
       </c>
       <c r="E444" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F444" s="3" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>35130000</v>
       </c>
       <c r="I444" s="5" t="n">
-        <v>38185</v>
+        <v>35060</v>
       </c>
       <c r="J444" s="3" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         </is>
       </c>
       <c r="E445" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F445" s="3" t="inlineStr">
         <is>
@@ -30683,7 +30683,7 @@
         <v>42280000</v>
       </c>
       <c r="I445" s="5" t="n">
-        <v>39294</v>
+        <v>36044</v>
       </c>
       <c r="J445" s="3" t="inlineStr">
         <is>
@@ -30733,7 +30733,7 @@
         </is>
       </c>
       <c r="E446" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F446" s="3" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>34980000</v>
       </c>
       <c r="I446" s="5" t="n">
-        <v>38022</v>
+        <v>34910</v>
       </c>
       <c r="J446" s="3" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         </is>
       </c>
       <c r="E448" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F448" s="3" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>34210000</v>
       </c>
       <c r="I448" s="5" t="n">
-        <v>37185</v>
+        <v>34142</v>
       </c>
       <c r="J448" s="3" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         </is>
       </c>
       <c r="E449" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F449" s="3" t="inlineStr">
         <is>
@@ -30947,7 +30947,7 @@
         <v>41880000</v>
       </c>
       <c r="I449" s="5" t="n">
-        <v>38922</v>
+        <v>35703</v>
       </c>
       <c r="J449" s="3" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         </is>
       </c>
       <c r="E451" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F451" s="3" t="inlineStr">
         <is>
@@ -31079,7 +31079,7 @@
         <v>40900000</v>
       </c>
       <c r="I451" s="5" t="n">
-        <v>38011</v>
+        <v>34868</v>
       </c>
       <c r="J451" s="3" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         </is>
       </c>
       <c r="E452" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F452" s="3" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>33800000</v>
       </c>
       <c r="I452" s="5" t="n">
-        <v>36739</v>
+        <v>33733</v>
       </c>
       <c r="J452" s="3" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         </is>
       </c>
       <c r="E454" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F454" s="3" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>33590000</v>
       </c>
       <c r="I454" s="5" t="n">
-        <v>36511</v>
+        <v>33523</v>
       </c>
       <c r="J454" s="3" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         </is>
       </c>
       <c r="E455" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F455" s="3" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>40370000</v>
       </c>
       <c r="I455" s="5" t="n">
-        <v>37519</v>
+        <v>34416</v>
       </c>
       <c r="J455" s="3" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         </is>
       </c>
       <c r="E456" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F456" s="3" t="inlineStr">
         <is>
@@ -31409,7 +31409,7 @@
         <v>33300000</v>
       </c>
       <c r="I456" s="5" t="n">
-        <v>36196</v>
+        <v>33234</v>
       </c>
       <c r="J456" s="3" t="inlineStr">
         <is>
@@ -31525,7 +31525,7 @@
         </is>
       </c>
       <c r="E458" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F458" s="3" t="inlineStr">
         <is>
@@ -31541,7 +31541,7 @@
         <v>33180000</v>
       </c>
       <c r="I458" s="5" t="n">
-        <v>36065</v>
+        <v>33114</v>
       </c>
       <c r="J458" s="3" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         </is>
       </c>
       <c r="E459" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F459" s="3" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>40870000</v>
       </c>
       <c r="I459" s="5" t="n">
-        <v>37983</v>
+        <v>34842</v>
       </c>
       <c r="J459" s="3" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         </is>
       </c>
       <c r="E461" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F461" s="3" t="inlineStr">
         <is>
@@ -31739,7 +31739,7 @@
         <v>39580000</v>
       </c>
       <c r="I461" s="5" t="n">
-        <v>36784</v>
+        <v>33743</v>
       </c>
       <c r="J461" s="3" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         </is>
       </c>
       <c r="E462" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>32710000</v>
       </c>
       <c r="I462" s="5" t="n">
-        <v>35554</v>
+        <v>32645</v>
       </c>
       <c r="J462" s="3" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         </is>
       </c>
       <c r="E463" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F463" s="3" t="inlineStr">
         <is>
@@ -31871,7 +31871,7 @@
         <v>39880000</v>
       </c>
       <c r="I463" s="5" t="n">
-        <v>37063</v>
+        <v>33998</v>
       </c>
       <c r="J463" s="3" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         </is>
       </c>
       <c r="E464" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F464" s="3" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>32950000</v>
       </c>
       <c r="I464" s="5" t="n">
-        <v>35815</v>
+        <v>32884</v>
       </c>
       <c r="J464" s="3" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         </is>
       </c>
       <c r="E465" s="4" t="n">
-        <v>1076</v>
+        <v>1173</v>
       </c>
       <c r="F465" s="3" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>40580000</v>
       </c>
       <c r="I465" s="5" t="n">
-        <v>37714</v>
+        <v>34595</v>
       </c>
       <c r="J465" s="3" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         </is>
       </c>
       <c r="E466" s="4" t="n">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="F466" s="3" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>34160000</v>
       </c>
       <c r="I466" s="5" t="n">
-        <v>37130</v>
+        <v>34092</v>
       </c>
       <c r="J466" s="3" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         </is>
       </c>
       <c r="E493" s="4" t="n">
-        <v>1165</v>
+        <v>1259</v>
       </c>
       <c r="F493" s="3" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>53810000</v>
       </c>
       <c r="I493" s="5" t="n">
-        <v>46189</v>
+        <v>42740</v>
       </c>
       <c r="J493" s="3" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         </is>
       </c>
       <c r="E501" s="4" t="n">
-        <v>1165</v>
+        <v>1259</v>
       </c>
       <c r="F501" s="3" t="inlineStr">
         <is>
@@ -34499,7 +34499,7 @@
         <v>48980000</v>
       </c>
       <c r="I501" s="5" t="n">
-        <v>42043</v>
+        <v>38904</v>
       </c>
       <c r="J501" s="3" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         </is>
       </c>
       <c r="E504" s="4" t="n">
-        <v>1204</v>
+        <v>1298</v>
       </c>
       <c r="F504" s="3" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>55300000</v>
       </c>
       <c r="I504" s="5" t="n">
-        <v>45930</v>
+        <v>42604</v>
       </c>
       <c r="J504" s="3" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         </is>
       </c>
       <c r="E505" s="4" t="n">
-        <v>1165</v>
+        <v>1259</v>
       </c>
       <c r="F505" s="3" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>54750000</v>
       </c>
       <c r="I505" s="5" t="n">
-        <v>46996</v>
+        <v>43487</v>
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         </is>
       </c>
       <c r="E516" s="4" t="n">
-        <v>1204</v>
+        <v>1298</v>
       </c>
       <c r="F516" s="3" t="inlineStr">
         <is>
@@ -35521,7 +35521,7 @@
         <v>51030000</v>
       </c>
       <c r="I516" s="5" t="n">
-        <v>42384</v>
+        <v>39314</v>
       </c>
       <c r="J516" s="3" t="inlineStr">
         <is>
@@ -35571,7 +35571,7 @@
         </is>
       </c>
       <c r="E517" s="4" t="n">
-        <v>1165</v>
+        <v>1259</v>
       </c>
       <c r="F517" s="3" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>49880000</v>
       </c>
       <c r="I517" s="5" t="n">
-        <v>42815</v>
+        <v>39619</v>
       </c>
       <c r="J517" s="3" t="inlineStr">
         <is>
@@ -36119,7 +36119,7 @@
         </is>
       </c>
       <c r="E525" s="4" t="n">
-        <v>1165</v>
+        <v>1259</v>
       </c>
       <c r="F525" s="3" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>51000000</v>
       </c>
       <c r="I525" s="5" t="n">
-        <v>43777</v>
+        <v>40508</v>
       </c>
       <c r="J525" s="3" t="inlineStr">
         <is>
@@ -36391,7 +36391,7 @@
         </is>
       </c>
       <c r="E529" s="4" t="n">
-        <v>1165</v>
+        <v>1259</v>
       </c>
       <c r="F529" s="3" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>48000000</v>
       </c>
       <c r="I529" s="5" t="n">
-        <v>41202</v>
+        <v>38125</v>
       </c>
       <c r="J529" s="3" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         </is>
       </c>
       <c r="E536" s="4" t="n">
-        <v>1204</v>
+        <v>1298</v>
       </c>
       <c r="F536" s="3" t="inlineStr">
         <is>
@@ -36893,7 +36893,7 @@
         <v>51530000</v>
       </c>
       <c r="I536" s="5" t="n">
-        <v>42799</v>
+        <v>39700</v>
       </c>
       <c r="J536" s="3" t="inlineStr">
         <is>
@@ -36943,7 +36943,7 @@
         </is>
       </c>
       <c r="E537" s="4" t="n">
-        <v>1165</v>
+        <v>1259</v>
       </c>
       <c r="F537" s="3" t="inlineStr">
         <is>
@@ -36959,7 +36959,7 @@
         <v>47500000</v>
       </c>
       <c r="I537" s="5" t="n">
-        <v>40773</v>
+        <v>37728</v>
       </c>
       <c r="J537" s="3" t="inlineStr">
         <is>
@@ -37215,7 +37215,7 @@
         </is>
       </c>
       <c r="E541" s="4" t="n">
-        <v>1165</v>
+        <v>1259</v>
       </c>
       <c r="F541" s="3" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45480000</v>
       </c>
       <c r="I541" s="5" t="n">
-        <v>39039</v>
+        <v>36124</v>
       </c>
       <c r="J541" s="3" t="inlineStr">
         <is>
@@ -37421,7 +37421,7 @@
         </is>
       </c>
       <c r="E544" s="4" t="n">
-        <v>1204</v>
+        <v>1298</v>
       </c>
       <c r="F544" s="3" t="inlineStr">
         <is>
@@ -37437,7 +37437,7 @@
         <v>49770000</v>
       </c>
       <c r="I544" s="5" t="n">
-        <v>41337</v>
+        <v>38344</v>
       </c>
       <c r="J544" s="3" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         </is>
       </c>
       <c r="E545" s="4" t="n">
-        <v>1165</v>
+        <v>1259</v>
       </c>
       <c r="F545" s="3" t="inlineStr">
         <is>
@@ -37503,7 +37503,7 @@
         <v>49300000</v>
       </c>
       <c r="I545" s="5" t="n">
-        <v>42318</v>
+        <v>39158</v>
       </c>
       <c r="J545" s="3" t="inlineStr">
         <is>
@@ -37693,7 +37693,7 @@
         </is>
       </c>
       <c r="E548" s="4" t="n">
-        <v>1204</v>
+        <v>1298</v>
       </c>
       <c r="F548" s="3" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>49000000</v>
       </c>
       <c r="I548" s="5" t="n">
-        <v>40698</v>
+        <v>37750</v>
       </c>
       <c r="J548" s="3" t="inlineStr">
         <is>
@@ -37759,7 +37759,7 @@
         </is>
       </c>
       <c r="E549" s="4" t="n">
-        <v>1165</v>
+        <v>1259</v>
       </c>
       <c r="F549" s="3" t="inlineStr">
         <is>
@@ -37775,7 +37775,7 @@
         <v>45500000</v>
       </c>
       <c r="I549" s="5" t="n">
-        <v>39056</v>
+        <v>36140</v>
       </c>
       <c r="J549" s="3" t="inlineStr">
         <is>
@@ -38031,7 +38031,7 @@
         </is>
       </c>
       <c r="E553" s="4" t="n">
-        <v>1165</v>
+        <v>1259</v>
       </c>
       <c r="F553" s="3" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45200000</v>
       </c>
       <c r="I553" s="5" t="n">
-        <v>38798</v>
+        <v>35902</v>
       </c>
       <c r="J553" s="3" t="inlineStr">
         <is>
@@ -38241,23 +38241,19 @@
       </c>
       <c r="F556" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G556" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H556" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I556" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="H556" s="5" t="n">
+        <v>47730000</v>
+      </c>
+      <c r="I556" s="5" t="n">
+        <v>36772</v>
       </c>
       <c r="J556" s="3" t="inlineStr">
         <is>
@@ -38266,12 +38262,12 @@
       </c>
       <c r="K556" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L556" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M556" s="3" t="inlineStr">
@@ -38281,7 +38277,7 @@
       </c>
       <c r="N556" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38307,7 +38303,7 @@
         </is>
       </c>
       <c r="E557" s="4" t="n">
-        <v>1165</v>
+        <v>1259</v>
       </c>
       <c r="F557" s="3" t="inlineStr">
         <is>
@@ -38323,7 +38319,7 @@
         <v>46350000</v>
       </c>
       <c r="I557" s="5" t="n">
-        <v>39785</v>
+        <v>36815</v>
       </c>
       <c r="J557" s="3" t="inlineStr">
         <is>
@@ -39227,9 +39223,9 @@
       <c r="C5" s="21" t="inlineStr"/>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1638万
-$27,768/呎
+$25,800/呎
 (26年-09月-07日)</t>
         </is>
       </c>
@@ -39258,9 +39254,9 @@
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1617万
-$27,399/呎
+$25,457/呎
 (26年-04月-23日)</t>
         </is>
       </c>
@@ -39289,9 +39285,9 @@
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1568万
-$26,576/呎
+$24,693/呎
 (26年-05月-06日)</t>
         </is>
       </c>
@@ -39320,9 +39316,9 @@
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1588万
-$26,907/呎
+$25,000/呎
 (26年-04月-02日)</t>
         </is>
       </c>
@@ -39351,9 +39347,9 @@
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1540万
-$26,099/呎
+$24,250/呎
 (26年-04月-17日)</t>
         </is>
       </c>
@@ -39366,9 +39362,9 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>A | 1339呎 (4+房)
+          <t>A | 1428呎 (4+房)
 $6740万
-$50,336/呎
+$47,199/呎
 (26年-06月-29日)</t>
         </is>
       </c>
@@ -39382,9 +39378,9 @@
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1575万
-$26,692/呎
+$24,800/呎
 (26年-04月-15日)</t>
         </is>
       </c>
@@ -39397,9 +39393,9 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>A | 1339呎 (4+房)
+          <t>A | 1428呎 (4+房)
 $6665万
-$49,776/呎
+$46,674/呎
 (26年-06月-17日)</t>
         </is>
       </c>
@@ -39413,9 +39409,9 @@
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1568万
-$26,584/呎
+$24,700/呎
 (26年-04月-16日)</t>
         </is>
       </c>
@@ -39428,9 +39424,9 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>A | 1339呎 (4+房)
+          <t>A | 1428呎 (4+房)
 $6007万
-$44,862/呎
+$42,066/呎
 (25年-06月-04日)</t>
         </is>
       </c>
@@ -39444,9 +39440,9 @@
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1562万
-$26,476/呎
+$24,600/呎
 (26年-03月-19日)</t>
         </is>
       </c>
@@ -39459,25 +39455,25 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>A | 1339呎 (4+房)
+          <t>A | 1428呎 (4+房)
 $6453万
-$48,193/呎
+$45,189/呎
 (26年-06月-04日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>B | 1171呎 (4+房)
+          <t>B | 1258呎 (4+房)
 $5285万
-$45,132/呎
+$42,011/呎
 (26年-06月-04日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1509万
-$25,577/呎
+$23,765/呎
 (26年-04月-14日)</t>
         </is>
       </c>
@@ -39498,17 +39494,17 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 1171呎 (4+房)
+          <t>B | 1258呎 (4+房)
 $4868万
-$41,571/呎
+$38,696/呎
 (25年-10月-21日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1497万
-$25,369/呎
+$23,572/呎
 (26年-03月-03日)</t>
         </is>
       </c>
@@ -39521,9 +39517,9 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>A | 1339呎 (4+房)
+          <t>A | 1428呎 (4+房)
 $5810万
-$43,391/呎
+$40,686/呎
 (25年-06月-04日)</t>
         </is>
       </c>
@@ -39537,9 +39533,9 @@
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1537万
-$26,046/呎
+$24,200/呎
 (26年-03月-11日)</t>
         </is>
       </c>
@@ -39552,25 +39548,25 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 1339呎 (4+房)
+          <t>A | 1428呎 (4+房)
 $6161万
-$46,012/呎
+$43,144/呎
 (26年-04月-17日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>B | 1171呎 (4+房)
+          <t>B | 1258呎 (4+房)
 $4900万
-$41,845/呎
+$38,951/呎
 (26年-02月-06日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1491万
-$25,264/呎
+$23,474/呎
 (26年-03月-13日)</t>
         </is>
       </c>
@@ -39591,17 +39587,17 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>B | 1171呎 (4+房)
+          <t>B | 1258呎 (4+房)
 $4756万
-$40,615/呎
+$37,806/呎
 (25年-11月-27日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1524万
-$25,831/呎
+$24,000/呎
 (26年-03月-03日)</t>
         </is>
       </c>
@@ -39614,25 +39610,25 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>A | 1339呎 (3房)
+          <t>A | 1428呎 (3房)
 $5832万
-$43,555/呎
+$40,840/呎
 (25年-12月-31日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>B | 1171呎 (4+房)
+          <t>B | 1258呎 (4+房)
 $4719万
-$40,299/呎
+$37,512/呎
 (25年-12月-31日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1465万
-$24,825/呎
+$23,066/呎
 (26年-02月-26日)</t>
         </is>
       </c>
@@ -39645,9 +39641,9 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>A | 1339呎 (4+房)
+          <t>A | 1428呎 (4+房)
 $5976万
-$44,630/呎
+$41,849/呎
 (26年-03月-30日)</t>
         </is>
       </c>
@@ -39661,9 +39657,9 @@
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1511万
-$25,615/呎
+$23,800/呎
 (26年-03月-17日)</t>
         </is>
       </c>
@@ -39684,17 +39680,17 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>B | 1171呎 (4+房)
+          <t>B | 1258呎 (4+房)
 $4568万
-$39,009/呎
+$36,312/呎
 (25年-06月-09日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1486万
-$25,185/呎
+$23,400/呎
 (26年-03月-02日)</t>
         </is>
       </c>
@@ -39707,25 +39703,25 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>A | 1339呎 (4+房)
+          <t>A | 1428呎 (4+房)
 $5550万
-$41,449/呎
+$38,866/呎
 (25年-05月-14日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>B | 1171呎 (4+房)
+          <t>B | 1258呎 (4+房)
 $4502万
-$38,446/呎
+$35,787/呎
 (25年-05月-14日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1461万
-$24,763/呎
+$23,008/呎
 (26年-03月-04日)</t>
         </is>
       </c>
@@ -39754,9 +39750,9 @@
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1405万
-$23,814/呎
+$22,126/呎
 (26年-04月-30日)</t>
         </is>
       </c>
@@ -39769,25 +39765,25 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>A | 1339呎 (4+房)
+          <t>A | 1428呎 (4+房)
 $5657万
-$42,248/呎
+$39,615/呎
 (25年-08月-19日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>B | 1171呎 (4+房)
+          <t>B | 1258呎 (4+房)
 $4790万
-$40,905/呎
+$38,076/呎
 (26年-08月-20日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1440万
-$24,410/呎
+$22,680/呎
 (26年-03月-03日)</t>
         </is>
       </c>
@@ -39808,17 +39804,17 @@
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>B | 1171呎 (4+房)
+          <t>B | 1258呎 (4+房)
 $4763万
-$40,675/呎
+$37,862/呎
 (26年-06月-16日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1422万
-$24,108/呎
+$22,400/呎
 (26年-02月-27日)</t>
         </is>
       </c>
@@ -39831,25 +39827,25 @@
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>A | 1339呎 (4+房)
+          <t>A | 1428呎 (4+房)
 $5468万
-$40,833/呎
+$38,288/呎
 (24年-12月-03日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>B | 1171呎 (4+房)
+          <t>B | 1258呎 (4+房)
 $4711万
-$40,231/呎
+$37,448/呎
 (26年-05月-07日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1416万
-$24,001/呎
+$22,300/呎
 (26年-02月-27日)</t>
         </is>
       </c>
@@ -39862,25 +39858,25 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>A | 1339呎 (4+房)
+          <t>A | 1428呎 (4+房)
 $5558万
-$41,509/呎
+$38,922/呎
 (25年-10月-14日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>B | 1171呎 (4+房)
+          <t>B | 1258呎 (4+房)
 $4510万
-$38,514/呎
+$35,851/呎
 (25年-11月-03日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1410万
-$23,893/呎
+$22,200/呎
 (26年-03月-09日)</t>
         </is>
       </c>
@@ -39893,25 +39889,25 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>A | 1339呎 (4+房)
+          <t>A | 1428呎 (4+房)
 $5546万
-$41,419/呎
+$38,838/呎
 (25年-11月-06日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>B | 1171呎 (4+房)
+          <t>B | 1258呎 (4+房)
 $4493万
-$38,369/呎
+$35,715/呎
 (25年-12月-11日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1407万
-$23,839/呎
+$22,150/呎
 (26年-03月-05日)</t>
         </is>
       </c>
@@ -39924,25 +39920,25 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>A | 1339呎 (4+房)
+          <t>A | 1428呎 (4+房)
 $5365万
-$40,067/呎
+$37,570/呎
 (25年-06月-12日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>B | 1171呎 (4+房)
+          <t>B | 1258呎 (4+房)
 $4557万
-$38,915/呎
+$36,224/呎
 (26年-04月-24日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1361万
-$23,072/呎
+$21,437/呎
 (26年-04月-02日)</t>
         </is>
       </c>
@@ -39955,25 +39951,25 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>A | 1339呎 (4+房)
+          <t>A | 1428呎 (4+房)
 $5432万
-$40,568/呎
+$38,039/呎
 (25年-11月-04日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>B | 1171呎 (4+房)
+          <t>B | 1258呎 (4+房)
 $4408万
-$37,643/呎
+$35,040/呎
 (25年-12月-05日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1397万
-$23,678/呎
+$22,000/呎
 (26年-04月-09日)</t>
         </is>
       </c>
@@ -39986,25 +39982,25 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>A | 1339呎 (4+房)
+          <t>A | 1428呎 (4+房)
 $5393万
-$40,275/呎
+$37,765/呎
 (25年-07月-30日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>B | 1171呎 (4+房)
+          <t>B | 1258呎 (4+房)
 $4379万
-$37,395/呎
+$34,809/呎
 (25年-10月-16日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1349万
-$22,864/呎
+$21,244/呎
 (26年-04月-14日)</t>
         </is>
       </c>
@@ -40017,25 +40013,25 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>A | 1339呎 (4+房)
+          <t>A | 1428呎 (4+房)
 $5327万
-$39,783/呎
+$37,304/呎
 (26年-02月-26日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>B | 1171呎 (4+房)
+          <t>B | 1258呎 (4+房)
 $4460万
-$38,087/呎
+$35,453/呎
 (26年-02月-04日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>C | 590呎 (3房)
+          <t>C | 635呎 (3房)
 $1324万
-$22,446/呎
+$20,855/呎
 (26年-04月-13日)</t>
         </is>
       </c>
@@ -40048,17 +40044,17 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>A | 1339呎 (4+房)
+          <t>A | 1428呎 (4+房)
 $5223万
-$39,007/呎
+$36,576/呎
 (26年-04月-13日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>B | 1171呎 (4+房)
+          <t>B | 1258呎 (4+房)
 $4412万
-$37,677/呎
+$35,072/呎
 (26年-03月-03日)</t>
         </is>
       </c>
@@ -40237,9 +40233,9 @@
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>B | 920呎 (3房)
+          <t>B | 1002呎 (3房)
 $4047万
-$43,989/呎
+$40,389/呎
 (26年-10月-14日)</t>
         </is>
       </c>
@@ -40260,9 +40256,9 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>B | 920呎 (3房)
+          <t>B | 1002呎 (3房)
 $3982万
-$43,283/呎
+$39,741/呎
 (26年-05月-28日)</t>
         </is>
       </c>
@@ -40283,9 +40279,9 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>B | 920呎 (3房)
+          <t>B | 1002呎 (3房)
 $3889万
-$42,272/呎
+$38,812/呎
 (26年-05月-26日)</t>
         </is>
       </c>
@@ -40306,9 +40302,9 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 920呎 (3房)
+          <t>B | 1002呎 (3房)
 $3638万
-$39,543/呎
+$36,307/呎
 (25年-11月-19日)</t>
         </is>
       </c>
@@ -40329,9 +40325,9 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>B | 920呎 (3房)
+          <t>B | 1002呎 (3房)
 $3610万
-$39,239/呎
+$36,028/呎
 (25年-12月-22日)</t>
         </is>
       </c>
@@ -40352,9 +40348,9 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>B | 920呎 (3房)
+          <t>B | 1002呎 (3房)
 $3454万
-$37,543/呎
+$34,471/呎
 (25年-03月-25日)</t>
         </is>
       </c>
@@ -40367,9 +40363,9 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>A | 1076呎 (4+房)
+          <t>A | 1173呎 (4+房)
 $4590万
-$42,658/呎
+$39,130/呎
 (26年-04月-15日)</t>
         </is>
       </c>
@@ -40390,9 +40386,9 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 1076呎 (4+房)
+          <t>A | 1173呎 (4+房)
 $4552万
-$42,305/呎
+$38,806/呎
 (26年-08月-14日)</t>
         </is>
       </c>
@@ -40436,17 +40432,17 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 1076呎 (4+房)
+          <t>A | 1173呎 (4+房)
 $4388万
-$40,781/呎
+$37,408/呎
 (26年-04月-02日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>B | 920呎 (3房)
+          <t>B | 1002呎 (3房)
 $3306万
-$35,935/呎
+$32,994/呎
 (24年-06月-04日)</t>
         </is>
       </c>
@@ -40459,9 +40455,9 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>A | 1076呎 (4+房)
+          <t>A | 1173呎 (4+房)
 $4365万
-$40,567/呎
+$37,212/呎
 (26年-04月-10日)</t>
         </is>
       </c>
@@ -40505,17 +40501,17 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>A | 1076呎 (4+房)
+          <t>A | 1173呎 (4+房)
 $4038万
-$37,528/呎
+$34,425/呎
 (25年-07月-04日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>B | 920呎 (3房)
+          <t>B | 1002呎 (3房)
 $3303万
-$35,902/呎
+$32,964/呎
 (24年-11月-22日)</t>
         </is>
       </c>
@@ -40605,9 +40601,9 @@
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>B | 920呎 (3房)
+          <t>B | 1002呎 (3房)
 $3140万
-$34,130/呎
+$31,337/呎
 (24年-03月-25日)</t>
         </is>
       </c>
@@ -40628,9 +40624,9 @@
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>B | 920呎 (3房)
+          <t>B | 1002呎 (3房)
 $3219万
-$34,989/呎
+$32,126/呎
 (25年-08月-27日)</t>
         </is>
       </c>
@@ -40689,9 +40685,9 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>A | 1076呎 (4+房)
+          <t>A | 1173呎 (4+房)
 $3836万
-$35,651/呎
+$32,702/呎
 (24年-04月-19日)</t>
         </is>
       </c>
@@ -40720,9 +40716,9 @@
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>B | 920呎 (3房)
+          <t>B | 1002呎 (3房)
 $3138万
-$34,109/呎
+$31,317/呎
 (25年-09月-04日)</t>
         </is>
       </c>
@@ -40743,9 +40739,9 @@
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>B | 920呎 (3房)
+          <t>B | 1002呎 (3房)
 $3044万
-$33,087/呎
+$30,379/呎
 (24年-05月-07日)</t>
         </is>
       </c>
@@ -40758,17 +40754,17 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>A | 1076呎 (4+房)
+          <t>A | 1173呎 (4+房)
 $3730万
-$34,667/呎
+$31,800/呎
 (24年-06月-06日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>B | 920呎 (3房)
+          <t>B | 1002呎 (3房)
 $3032万
-$32,957/呎
+$30,259/呎
 (24年-05月-21日)</t>
         </is>
       </c>
@@ -40781,17 +40777,17 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>A | 1076呎 (4+房)
+          <t>A | 1173呎 (4+房)
 $3715万
-$34,526/呎
+$31,671/呎
 (25年-03月-26日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>B | 920呎 (3房)
+          <t>B | 1002呎 (3房)
 $3028万
-$32,913/呎
+$30,220/呎
 (25年-04月-02日)</t>
         </is>
       </c>
@@ -40804,9 +40800,9 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>A | 1076呎 (4+房)
+          <t>A | 1173呎 (4+房)
 $3651万
-$33,931/呎
+$31,125/呎
 (25年-05月-21日)</t>
         </is>
       </c>
@@ -41185,9 +41181,9 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>B | 994呎 (3房)
+          <t>B | 1085呎 (3房)
 $4060万
-$40,845/呎
+$37,419/呎
 (25年-12月-17日)</t>
         </is>
       </c>
@@ -41216,17 +41212,17 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>A | 1027呎 (3房)
+          <t>A | 1102呎 (3房)
 $4163万
-$40,537/呎
+$37,779/呎
 (26年-08月-21日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>B | 994呎 (3房)
+          <t>B | 1085呎 (3房)
 $3860万
-$38,833/呎
+$35,576/呎
 (25年-01月-15日)</t>
         </is>
       </c>
@@ -41255,9 +41251,9 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>A | 1027呎 (3房)
+          <t>A | 1102呎 (3房)
 $3774万
-$36,748/呎
+$34,247/呎
 (24年-11月-22日)</t>
         </is>
       </c>
@@ -41302,9 +41298,9 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 994呎 (3房)
+          <t>B | 1085呎 (3房)
 $3752万
-$37,746/呎
+$34,581/呎
 (25年-01月-10日)</t>
         </is>
       </c>
@@ -41333,17 +41329,17 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>A | 1027呎 (3房)
+          <t>A | 1102呎 (3房)
 $3680万
-$35,833/呎
+$33,394/呎
 (24年-04月-29日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>B | 994呎 (3房)
+          <t>B | 1085呎 (3房)
 $3660万
-$36,821/呎
+$33,733/呎
 (24年-04月-29日)</t>
         </is>
       </c>
@@ -41411,17 +41407,17 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>A | 1027呎 (3房)
+          <t>A | 1102呎 (3房)
 $4114万
-$40,057/呎
+$37,331/呎
 (26年-04月-30日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>B | 994呎 (3房)
+          <t>B | 1085呎 (3房)
 $4960万
-$49,899/呎
+$45,714/呎
 (26年-06月-24日)</t>
         </is>
       </c>
@@ -41458,9 +41454,9 @@
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>B | 994呎 (3房)
+          <t>B | 1085呎 (3房)
 $3629万
-$36,509/呎
+$33,447/呎
 (24年-12月-06日)</t>
         </is>
       </c>
@@ -41528,9 +41524,9 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>A | 1027呎 (3房)
+          <t>A | 1102呎 (3房)
 $3584万
-$34,898/呎
+$32,523/呎
 (24年-12月-03日)</t>
         </is>
       </c>
@@ -41567,9 +41563,9 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>A | 1027呎 (3房)
+          <t>A | 1102呎 (3房)
 $3563万
-$34,693/呎
+$32,332/呎
 (24年-11月-19日)</t>
         </is>
       </c>
@@ -41606,17 +41602,17 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>A | 1027呎 (3房)
+          <t>A | 1102呎 (3房)
 $3593万
-$34,985/呎
+$32,604/呎
 (25年-09月-18日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>B | 994呎 (3房)
+          <t>B | 1085呎 (3房)
 $3540万
-$35,611/呎
+$32,625/呎
 (24年-11月-22日)</t>
         </is>
       </c>
@@ -41723,17 +41719,17 @@
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>A | 1027呎 (3房)
+          <t>A | 1102呎 (3房)
 $3880万
-$37,780/呎
+$35,209/呎
 (26年-04月-16日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>B | 994呎 (3房)
+          <t>B | 1085呎 (3房)
 $3555万
-$35,765/呎
+$32,765/呎
 (24年-12月-04日)</t>
         </is>
       </c>
@@ -41770,9 +41766,9 @@
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>B | 994呎 (3房)
+          <t>B | 1085呎 (3房)
 $3454万
-$34,744/呎
+$31,830/呎
 (24年-11月-18日)</t>
         </is>
       </c>
@@ -41926,9 +41922,9 @@
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>B | 994呎 (3房)
+          <t>B | 1085呎 (3房)
 $3351万
-$33,712/呎
+$30,885/呎
 (24年-12月-06日)</t>
         </is>
       </c>
@@ -41957,9 +41953,9 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>A | 1027呎 (3房)
+          <t>A | 1102呎 (3房)
 $3323万
-$32,356/呎
+$30,154/呎
 (25年-04月-08日)</t>
         </is>
       </c>
@@ -42004,9 +42000,9 @@
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>B | 994呎 (3房)
+          <t>B | 1085呎 (3房)
 $3530万
-$35,513/呎
+$32,535/呎
 (26年-04月-23日)</t>
         </is>
       </c>
@@ -42269,9 +42265,9 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 1282呎 (4+房)
+          <t>B | 1382呎 (4+房)
 $5982万
-$46,661/呎
+$43,285/呎
 (26年-06月-08日)</t>
         </is>
       </c>
@@ -42284,9 +42280,9 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>A | 1282呎 (4+房)
+          <t>A | 1382呎 (4+房)
 $5591万
-$43,612/呎
+$40,456/呎
 (25年-11月-27日)</t>
         </is>
       </c>
@@ -42338,9 +42334,9 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>B | 1282呎 (4+房)
+          <t>B | 1382呎 (4+房)
 $5432万
-$42,371/呎
+$39,305/呎
 (25年-09月-10日)</t>
         </is>
       </c>
@@ -42384,9 +42380,9 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>B | 1282呎 (4+房)
+          <t>B | 1382呎 (4+房)
 $5226万
-$40,767/呎
+$37,817/呎
 (24年-12月-11日)</t>
         </is>
       </c>
@@ -42399,17 +42395,17 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 1282呎 (4+房)
+          <t>A | 1382呎 (4+房)
 $5195万
-$40,523/呎
+$37,590/呎
 (25年-05月-06日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>B | 1282呎 (4+房)
+          <t>B | 1382呎 (4+房)
 $5195万
-$40,523/呎
+$37,590/呎
 (25年-06月-06日)</t>
         </is>
       </c>
@@ -42445,9 +42441,9 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>A | 1282呎 (4+房)
+          <t>A | 1382呎 (4+房)
 $5246万
-$40,919/呎
+$37,958/呎
 (25年-11月-05日)</t>
         </is>
       </c>
@@ -42468,9 +42464,9 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>A | 1282呎 (4+房)
+          <t>A | 1382呎 (4+房)
 $5428万
-$42,340/呎
+$39,276/呎
 (26年-02月-24日)</t>
         </is>
       </c>
@@ -42537,17 +42533,17 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>A | 1282呎 (4+房)
+          <t>A | 1382呎 (4+房)
 $5070万
-$39,548/呎
+$36,686/呎
 (25年-08月-20日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>B | 1282呎 (4+房)
+          <t>B | 1382呎 (4+房)
 $5070万
-$39,548/呎
+$36,686/呎
 (25年-09月-01日)</t>
         </is>
       </c>
@@ -42560,17 +42556,17 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>A | 1282呎 (4+房)
+          <t>A | 1382呎 (4+房)
 $4981万
-$38,853/呎
+$36,042/呎
 (25年-04月-24日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>B | 1282呎 (4+房)
+          <t>B | 1382呎 (4+房)
 $5060万
-$39,470/呎
+$36,614/呎
 (25年-08月-11日)</t>
         </is>
       </c>
@@ -42583,17 +42579,17 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>A | 1282呎 (4+房)
+          <t>A | 1382呎 (4+房)
 $5050万
-$39,392/呎
+$36,541/呎
 (25年-11月-25日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>B | 1282呎 (4+房)
+          <t>B | 1382呎 (4+房)
 $5050万
-$39,392/呎
+$36,541/呎
 (25年-10月-13日)</t>
         </is>
       </c>
@@ -42606,17 +42602,17 @@
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>A | 1282呎 (4+房)
+          <t>A | 1382呎 (4+房)
 $4898万
-$38,206/呎
+$35,441/呎
 (25年-05月-08日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>B | 1282呎 (4+房)
+          <t>B | 1382呎 (4+房)
 $4898万
-$38,206/呎
+$35,441/呎
 (25年-05月-08日)</t>
         </is>
       </c>
@@ -42629,9 +42625,9 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>A | 1282呎 (4+房)
+          <t>A | 1382呎 (4+房)
 $4995万
-$38,963/呎
+$36,143/呎
 (25年-10月-17日)</t>
         </is>
       </c>
@@ -42652,17 +42648,17 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>A | 1282呎 (4+房)
+          <t>A | 1382呎 (4+房)
 $4966万
-$38,736/呎
+$35,933/呎
 (25年-10月-14日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>B | 1282呎 (4+房)
+          <t>B | 1382呎 (4+房)
 $4966万
-$38,736/呎
+$35,933/呎
 (25年-10月-14日)</t>
         </is>
       </c>
@@ -42675,17 +42671,17 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>A | 1282呎 (4+房)
+          <t>A | 1382呎 (4+房)
 $4908万
-$38,284/呎
+$35,514/呎
 (25年-10月-30日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>B | 1282呎 (4+房)
+          <t>B | 1382呎 (4+房)
 $4908万
-$38,284/呎
+$35,514/呎
 (25年-10月-30日)</t>
         </is>
       </c>
@@ -42698,17 +42694,17 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>A | 1282呎 (4+房)
+          <t>A | 1382呎 (4+房)
 $4814万
-$37,549/呎
+$34,832/呎
 (25年-10月-17日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>B | 1282呎 (4+房)
+          <t>B | 1382呎 (4+房)
 $4819万
-$37,590/呎
+$34,870/呎
 (25年-11月-12日)</t>
         </is>
       </c>
@@ -42721,17 +42717,17 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>A | 1282呎 (4+房)
+          <t>A | 1382呎 (4+房)
 $4845万
-$37,793/呎
+$35,058/呎
 (25年-11月-25日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>B | 1282呎 (4+房)
+          <t>B | 1382呎 (4+房)
 $4961万
-$38,697/呎
+$35,897/呎
 (25年-12月-24日)</t>
         </is>
       </c>
@@ -42744,17 +42740,17 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>A | 1282呎 (4+房)
+          <t>A | 1382呎 (4+房)
 $4882万
-$38,081/呎
+$35,326/呎
 (26年-04月-15日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>B | 1282呎 (4+房)
+          <t>B | 1382呎 (4+房)
 $4753万
-$37,075/呎
+$34,392/呎
 (25年-11月-04日)</t>
         </is>
       </c>
@@ -42767,17 +42763,17 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>A | 1282呎 (4+房)
+          <t>A | 1382呎 (4+房)
 $4868万
-$37,972/呎
+$35,224/呎
 (26年-05月-18日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>B | 1282呎 (4+房)
+          <t>B | 1382呎 (4+房)
 $4877万
-$38,042/呎
+$35,289/呎
 (26年-05月-04日)</t>
         </is>
       </c>
@@ -43140,17 +43136,17 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 1085呎 (3房)
 $4469万
-$45,050/呎
+$41,189/呎
 (26年-06月-30日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>B | 1027呎 (3房)
+          <t>B | 1102呎 (3房)
 $4518万
-$43,992/呎
+$40,998/呎
 (26年-06月-30日)</t>
         </is>
       </c>
@@ -43179,9 +43175,9 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 1085呎 (3房)
 $4405万
-$44,405/呎
+$40,599/呎
 (26年-04月-17日)</t>
         </is>
       </c>
@@ -43218,17 +43214,17 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 1085呎 (3房)
 $4341万
-$43,760/呎
+$40,009/呎
 (26年-05月-18日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>B | 1027呎 (3房)
+          <t>B | 1102呎 (3房)
 $4427万
-$43,106/呎
+$40,172/呎
 (26年-05月-18日)</t>
         </is>
       </c>
@@ -43257,17 +43253,17 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 1085呎 (3房)
 $4217万
-$42,510/呎
+$38,866/呎
 (26年-02月-25日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 1027呎 (3房)
+          <t>B | 1102呎 (3房)
 $4378万
-$42,629/呎
+$39,728/呎
 (26年-10月-23日)</t>
         </is>
       </c>
@@ -43296,17 +43292,17 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 1085呎 (3房)
 $3865万
-$38,962/呎
+$35,622/呎
 (25年-09月-16日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>B | 1027呎 (3房)
+          <t>B | 1102呎 (3房)
 $4300万
-$41,870/呎
+$39,020/呎
 (26年-05月-22日)</t>
         </is>
       </c>
@@ -43335,17 +43331,17 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 1085呎 (3房)
 $3843万
-$38,740/呎
+$35,419/呎
 (25年-10月-24日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>B | 1027呎 (3房)
+          <t>B | 1102呎 (3房)
 $3885万
-$37,829/呎
+$35,254/呎
 (25年-10月-24日)</t>
         </is>
       </c>
@@ -43374,17 +43370,17 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 1085呎 (3房)
 $3898万
-$39,294/呎
+$35,926/呎
 (25年-11月-25日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>B | 1027呎 (3房)
+          <t>B | 1102呎 (3房)
 $4129万
-$40,204/呎
+$37,468/呎
 (26年-05月-22日)</t>
         </is>
       </c>
@@ -43413,17 +43409,17 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 1085呎 (3房)
 $3820万
-$38,508/呎
+$35,207/呎
 (25年-10月-13日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>B | 1027呎 (3房)
+          <t>B | 1102呎 (3房)
 $3935万
-$38,315/呎
+$35,708/呎
 (25年-12月-10日)</t>
         </is>
       </c>
@@ -43452,17 +43448,17 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 1085呎 (3房)
 $3818万
-$38,488/呎
+$35,189/呎
 (25年-11月-10日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>B | 1027呎 (3房)
+          <t>B | 1102呎 (3房)
 $3878万
-$37,760/呎
+$35,191/呎
 (25年-12月-04日)</t>
         </is>
       </c>
@@ -43530,17 +43526,17 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 1085呎 (3房)
 $3740万
-$37,702/呎
+$34,470/呎
 (25年-10月-14日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>B | 1027呎 (3房)
+          <t>B | 1102呎 (3房)
 $3780万
-$36,806/呎
+$34,301/呎
 (25年-09月-10日)</t>
         </is>
       </c>
@@ -43569,17 +43565,17 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 1085呎 (3房)
 $3730万
-$37,601/呎
+$34,378/呎
 (25年-10月-10日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>B | 1027呎 (3房)
+          <t>B | 1102呎 (3房)
 $3700万
-$36,027/呎
+$33,575/呎
 (25年-07月-14日)</t>
         </is>
       </c>
@@ -43608,17 +43604,17 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 1085呎 (3房)
 $3679万
-$37,087/呎
+$33,908/呎
 (25年-06月-27日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>B | 1027呎 (3房)
+          <t>B | 1102呎 (3房)
 $3728万
-$36,300/呎
+$33,829/呎
 (25年-07月-14日)</t>
         </is>
       </c>
@@ -43647,17 +43643,17 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 1085呎 (3房)
 $3600万
-$36,290/呎
+$33,180/呎
 (25年-06月-13日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>B | 1027呎 (3房)
+          <t>B | 1102呎 (3房)
 $3640万
-$35,443/呎
+$33,031/呎
 (25年-05月-06日)</t>
         </is>
       </c>
@@ -43725,9 +43721,9 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 1085呎 (3房)
 $3565万
-$35,938/呎
+$32,857/呎
 (25年-04月-25日)</t>
         </is>
       </c>
@@ -43764,17 +43760,17 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 1085呎 (3房)
 $3626万
-$36,552/呎
+$33,419/呎
 (25年-08月-20日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>B | 1027呎 (3房)
+          <t>B | 1102呎 (3房)
 $3664万
-$35,677/呎
+$33,249/呎
 (25年-08月-20日)</t>
         </is>
       </c>
@@ -43803,17 +43799,17 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 1085呎 (3房)
 $3453万
-$34,808/呎
+$31,825/呎
 (25年-05月-27日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>B | 1027呎 (3房)
+          <t>B | 1102呎 (3房)
 $3653万
-$35,570/呎
+$33,149/呎
 (25年-09月-02日)</t>
         </is>
       </c>
@@ -43842,17 +43838,17 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 1085呎 (3房)
 $3274万
-$33,004/呎
+$30,175/呎
 (25年-04月-08日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>B | 1042呎 (3房)
+          <t>B | 1117呎 (3房)
 $3771万
-$36,190/呎
+$33,760/呎
 (26年-04月-30日)</t>
         </is>
       </c>
@@ -43889,9 +43885,9 @@
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>B | 1042呎 (3房)
+          <t>B | 1117呎 (3房)
 $3193万
-$30,643/呎
+$28,585/呎
 (25年-04月-17日)</t>
         </is>
       </c>
@@ -43920,9 +43916,9 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 1085呎 (3房)
 $3184万
-$32,097/呎
+$29,346/呎
 (25年-04月-08日)</t>
         </is>
       </c>
@@ -44201,9 +44197,9 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 1002呎 (3房)
 $4111万
-$44,685/呎
+$41,028/呎
 (26年-06月-01日)</t>
         </is>
       </c>
@@ -44224,17 +44220,17 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 1002呎 (3房)
 $3835万
-$41,685/呎
+$38,273/呎
 (26年-01月-23日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 1076呎 (4+房)
+          <t>B | 1173呎 (4+房)
 $4636万
-$43,086/呎
+$39,523/呎
 (26年-01月-23日)</t>
         </is>
       </c>
@@ -44247,17 +44243,17 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 1002呎 (3房)
 $3675万
-$39,946/呎
+$36,677/呎
 (25年-11月-04日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>B | 1076呎 (4+房)
+          <t>B | 1173呎 (4+房)
 $4430万
-$41,171/呎
+$37,766/呎
 (25年-11月-04日)</t>
         </is>
       </c>
@@ -44270,17 +44266,17 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 1002呎 (3房)
 $3643万
-$39,598/呎
+$36,357/呎
 (25年-10月-15日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>B | 1076呎 (4+房)
+          <t>B | 1173呎 (4+房)
 $4405万
-$40,939/呎
+$37,553/呎
 (25年-10月-15日)</t>
         </is>
       </c>
@@ -44316,17 +44312,17 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 1002呎 (3房)
 $3580万
-$38,913/呎
+$35,729/呎
 (25年-08月-06日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 1076呎 (4+房)
+          <t>B | 1173呎 (4+房)
 $4345万
-$40,381/呎
+$37,042/呎
 (25年-08月-18日)</t>
         </is>
       </c>
@@ -44339,17 +44335,17 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 1002呎 (3房)
 $3534万
-$38,413/呎
+$35,269/呎
 (25年-07月-24日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>B | 1076呎 (4+房)
+          <t>B | 1173呎 (4+房)
 $4298万
-$39,944/呎
+$36,641/呎
 (25年-11月-06日)</t>
         </is>
       </c>
@@ -44362,9 +44358,9 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 1002呎 (3房)
 $3472万
-$37,739/呎
+$34,651/呎
 (25年-06月-10日)</t>
         </is>
       </c>
@@ -44385,17 +44381,17 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 1002呎 (3房)
 $3513万
-$38,185/呎
+$35,060/呎
 (25年-08月-27日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>B | 1076呎 (4+房)
+          <t>B | 1173呎 (4+房)
 $4246万
-$39,461/呎
+$36,198/呎
 (25年-08月-27日)</t>
         </is>
       </c>
@@ -44408,17 +44404,17 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 1002呎 (3房)
 $3498万
-$38,022/呎
+$34,910/呎
 (25年-08月-27日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>B | 1076呎 (4+房)
+          <t>B | 1173呎 (4+房)
 $4228万
-$39,294/呎
+$36,044/呎
 (25年-07月-25日)</t>
         </is>
       </c>
@@ -44431,9 +44427,9 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 1002呎 (3房)
 $3421万
-$37,185/呎
+$34,142/呎
 (25年-04月-15日)</t>
         </is>
       </c>
@@ -44462,9 +44458,9 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>B | 1076呎 (4+房)
+          <t>B | 1173呎 (4+房)
 $4188万
-$38,922/呎
+$35,703/呎
 (25年-10月-24日)</t>
         </is>
       </c>
@@ -44477,17 +44473,17 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 1002呎 (3房)
 $3380万
-$36,739/呎
+$33,733/呎
 (25年-06月-06日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>B | 1076呎 (4+房)
+          <t>B | 1173呎 (4+房)
 $4090万
-$38,011/呎
+$34,868/呎
 (25年-05月-28日)</t>
         </is>
       </c>
@@ -44500,9 +44496,9 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 1002呎 (3房)
 $3359万
-$36,511/呎
+$33,523/呎
 (25年-04月-30日)</t>
         </is>
       </c>
@@ -44523,17 +44519,17 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 1002呎 (3房)
 $3330万
-$36,196/呎
+$33,234/呎
 (24年-12月-31日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>B | 1076呎 (4+房)
+          <t>B | 1173呎 (4+房)
 $4037万
-$37,519/呎
+$34,416/呎
 (25年-06月-05日)</t>
         </is>
       </c>
@@ -44546,9 +44542,9 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 1002呎 (3房)
 $3318万
-$36,065/呎
+$33,114/呎
 (24年-12月-20日)</t>
         </is>
       </c>
@@ -44577,9 +44573,9 @@
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>B | 1076呎 (3房)
+          <t>B | 1173呎 (3房)
 $4087万
-$37,983/呎
+$34,842/呎
 (25年-10月-14日)</t>
         </is>
       </c>
@@ -44592,17 +44588,17 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 1002呎 (3房)
 $3271万
-$35,554/呎
+$32,645/呎
 (25年-04月-30日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>B | 1076呎 (4+房)
+          <t>B | 1173呎 (4+房)
 $3958万
-$36,784/呎
+$33,743/呎
 (25年-06月-04日)</t>
         </is>
       </c>
@@ -44615,17 +44611,17 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 1002呎 (3房)
 $3295万
-$35,815/呎
+$32,884/呎
 (25年-09月-04日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>B | 1076呎 (4+房)
+          <t>B | 1173呎 (4+房)
 $3988万
-$37,063/呎
+$33,998/呎
 (25年-10月-14日)</t>
         </is>
       </c>
@@ -44638,17 +44634,17 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>A | 920呎 (3房)
+          <t>A | 1002呎 (3房)
 $3416万
-$37,130/呎
+$34,092/呎
 (25年-12月-17日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>B | 1076呎 (4+房)
+          <t>B | 1173呎 (4+房)
 $4058万
-$37,714/呎
+$34,595/呎
 (26年-07月-08日)</t>
         </is>
       </c>
@@ -44725,7 +44721,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -44735,7 +44731,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -45011,9 +45007,9 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>A | 1165呎 (4+房)
+          <t>A | 1259呎 (4+房)
 $5381万
-$46,189/呎
+$42,740/呎
 (26年-04月-24日)</t>
         </is>
       </c>
@@ -45089,9 +45085,9 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>A | 1165呎 (4+房)
+          <t>A | 1259呎 (4+房)
 $4898万
-$42,043/呎
+$38,904/呎
 (25年-09月-22日)</t>
         </is>
       </c>
@@ -45128,17 +45124,17 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 1165呎 (4+房)
+          <t>A | 1259呎 (4+房)
 $5475万
-$46,996/呎
+$43,487/呎
 (26年-08月-18日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>B | 1204呎 (4+房)
+          <t>B | 1298呎 (4+房)
 $5530万
-$45,930/呎
+$42,604/呎
 (26年-08月-24日)</t>
         </is>
       </c>
@@ -45245,17 +45241,17 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>A | 1165呎 (4+房)
+          <t>A | 1259呎 (4+房)
 $4988万
-$42,815/呎
+$39,619/呎
 (26年-02月-04日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>B | 1204呎 (4+房)
+          <t>B | 1298呎 (4+房)
 $5103万
-$42,384/呎
+$39,314/呎
 (26年-02月-04日)</t>
         </is>
       </c>
@@ -45323,9 +45319,9 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>A | 1165呎 (4+房)
+          <t>A | 1259呎 (4+房)
 $5100万
-$43,777/呎
+$40,508/呎
 (26年-10月-08日)</t>
         </is>
       </c>
@@ -45362,9 +45358,9 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>A | 1165呎 (4+房)
+          <t>A | 1259呎 (4+房)
 $4800万
-$41,202/呎
+$38,125/呎
 (26年-03月-23日)</t>
         </is>
       </c>
@@ -45440,17 +45436,17 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>A | 1165呎 (4+房)
+          <t>A | 1259呎 (4+房)
 $4750万
-$40,773/呎
+$37,728/呎
 (26年-02月-10日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>B | 1204呎 (4+房)
+          <t>B | 1298呎 (4+房)
 $5153万
-$42,799/呎
+$39,700/呎
 (26年-05月-22日)</t>
         </is>
       </c>
@@ -45479,9 +45475,9 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>A | 1165呎 (4+房)
+          <t>A | 1259呎 (4+房)
 $4548万
-$39,039/呎
+$36,124/呎
 (25年-09月-16日)</t>
         </is>
       </c>
@@ -45518,17 +45514,17 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>A | 1165呎 (4+房)
+          <t>A | 1259呎 (4+房)
 $4930万
-$42,318/呎
+$39,158/呎
 (26年-06月-02日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>B | 1204呎 (4+房)
+          <t>B | 1298呎 (4+房)
 $4977万
-$41,337/呎
+$38,344/呎
 (26年-06月-02日)</t>
         </is>
       </c>
@@ -45557,17 +45553,17 @@
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>A | 1165呎 (4+房)
+          <t>A | 1259呎 (4+房)
 $4550万
-$39,056/呎
+$36,140/呎
 (26年-02月-23日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>B | 1204呎 (4+房)
+          <t>B | 1298呎 (4+房)
 $4900万
-$40,698/呎
+$37,750/呎
 (26年-07月-09日)</t>
         </is>
       </c>
@@ -45596,9 +45592,9 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>A | 1165呎 (4+房)
+          <t>A | 1259呎 (4+房)
 $4520万
-$38,798/呎
+$35,902/呎
 (26年-01月-27日)</t>
         </is>
       </c>
@@ -45635,18 +45631,18 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>A | 1165呎 (4+房)
+          <t>A | 1259呎 (4+房)
 $4635万
-$39,785/呎
+$36,815/呎
 (26年-10月-14日)</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 1298呎 (4+房)
-招标单位
--
-(在售)</t>
+$4773万
+$36,772/呎
+(26年-10月-29日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
